--- a/project/src/main/resources/static/templates/后工序.xlsx
+++ b/project/src/main/resources/static/templates/后工序.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="166">
   <si>
     <t>安徽江福科技有限公司</t>
   </si>
@@ -395,6 +395,9 @@
   </si>
   <si>
     <t>侧修边冲孔需要线切割的镶块安装面必须和斜楔冲压方向一致，以保证能够线切割；</t>
+  </si>
+  <si>
+    <t>/</t>
   </si>
   <si>
     <t>定位键槽靠侧壁的一端，距侧壁的距离要≥35mm，除非侧壁高度小于45mm；</t>
@@ -512,7 +515,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -533,6 +536,11 @@
     </font>
     <font>
       <color rgb="FF000000"/>
+      <sz val="11"/>
+      <name val="宋体"/>
+    </font>
+    <font>
+      <color rgb="FF000000"/>
       <sz val="12"/>
       <name val="宋体"/>
     </font>
@@ -549,12 +557,6 @@
       <name val="宋体"/>
     </font>
     <font>
-      <color rgb="FF000000"/>
-      <sz val="11"/>
-      <name val="宋体"/>
-    </font>
-    <font>
-      <u/>
       <color rgb="FF800080"/>
       <sz val="24"/>
       <name val="宋体"/>
@@ -587,12 +589,18 @@
     </font>
     <font>
       <b/>
+      <color rgb="FF000000"/>
+      <sz val="10"/>
+      <name val="宋体"/>
+    </font>
+    <font>
+      <b/>
       <color rgb="FFFF0000"/>
       <sz val="10"/>
       <name val="宋体"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -614,6 +622,11 @@
         <fgColor rgb="FFFFC000"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFd9d9d9"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -627,10 +640,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="bottom" wrapText="1"/>
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -638,37 +651,38 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -680,13 +694,13 @@
     <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -701,13 +715,13 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1049,22 +1063,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:R150"/>
+  <dimension ref="A1:R105"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="11.066666666666666" customWidth="1"/>
-    <col min="2" max="2" width="26.933333333333334" customWidth="1"/>
-    <col min="3" max="3" width="11.466666666666667" customWidth="1"/>
-    <col min="4" max="4" width="96.53333333333333" customWidth="1"/>
+    <col min="1" max="1" width="11.6" customWidth="1"/>
+    <col min="2" max="2" width="28.4" customWidth="1"/>
+    <col min="3" max="3" width="12" customWidth="1"/>
+    <col min="4" max="4" width="102.8" customWidth="1"/>
     <col min="5" max="10" width="4.933333333333334" customWidth="1"/>
-    <col min="11" max="11" width="9.866666666666667" customWidth="1"/>
-    <col min="12" max="12" width="11.466666666666667" customWidth="1"/>
+    <col min="11" max="11" width="10.266666666666667" customWidth="1"/>
+    <col min="12" max="12" width="12" customWidth="1"/>
     <col min="13" max="15" width="4.933333333333334" customWidth="1"/>
-    <col min="16" max="17" width="7.866666666666666" customWidth="1"/>
-    <col min="18" max="18" width="5.866666666666666" customWidth="1"/>
+    <col min="16" max="17" width="8.133333333333333" customWidth="1"/>
+    <col min="18" max="18" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="20.25" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" ht="16.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -1075,1588 +1089,1609 @@
         <v>1</v>
       </c>
       <c r="F1" s="3"/>
-      <c r="H1"/>
-      <c r="I1"/>
-      <c r="J1"/>
-      <c r="K1"/>
-      <c r="L1" s="4" t="s">
+      <c r="G1" s="4"/>
+      <c r="H1" s="4"/>
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
+      <c r="K1" s="4"/>
+      <c r="L1" s="5" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" ht="20.25" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" ht="16.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
       <c r="D2" s="2"/>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="5"/>
-      <c r="G2" s="6">
-        <f>[40]目录!H10</f>
-      </c>
-      <c r="H2" s="6"/>
-      <c r="I2" s="6"/>
-      <c r="J2" s="6"/>
-      <c r="K2" s="6"/>
-      <c r="L2" s="7">
-        <f>[40]目录!J10</f>
-      </c>
-    </row>
-    <row r="3" ht="20.25" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="F2" s="6"/>
+      <c r="G2" s="7"/>
+      <c r="H2" s="7"/>
+      <c r="I2" s="7"/>
+      <c r="J2" s="7"/>
+      <c r="K2" s="7"/>
+      <c r="L2" s="8"/>
+    </row>
+    <row r="3" ht="16.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
       <c r="D3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="5"/>
-      <c r="G3" s="6">
-        <f>[40]目录!H11</f>
-      </c>
-      <c r="H3" s="6"/>
-      <c r="I3" s="6"/>
-      <c r="J3" s="6"/>
-      <c r="K3" s="6"/>
-      <c r="L3" s="7">
-        <f>[40]目录!J11</f>
-      </c>
-    </row>
-    <row r="4" ht="20.25" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" s="8" t="s">
+      <c r="F3" s="6"/>
+      <c r="G3" s="7"/>
+      <c r="H3" s="7"/>
+      <c r="I3" s="7"/>
+      <c r="J3" s="7"/>
+      <c r="K3" s="7"/>
+      <c r="L3" s="8"/>
+    </row>
+    <row r="4" ht="16.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A4" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="8">
-        <f>[40]目录!H5</f>
-      </c>
-      <c r="C4" s="8" t="s">
+      <c r="B4" s="9"/>
+      <c r="C4" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="7">
-        <f>[40]目录!H7</f>
-      </c>
-      <c r="E4" s="5" t="s">
+      <c r="D4" s="8"/>
+      <c r="E4" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="F4" s="5"/>
-      <c r="G4" s="6">
-        <f>[40]目录!H12</f>
-      </c>
-      <c r="H4" s="6"/>
-      <c r="I4" s="6"/>
-      <c r="J4" s="6"/>
-      <c r="K4" s="6"/>
-      <c r="L4" s="7">
-        <f>[40]目录!J12</f>
-      </c>
-    </row>
-    <row r="5" ht="17.25" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" s="8" t="s">
+      <c r="F4" s="6"/>
+      <c r="G4" s="7"/>
+      <c r="H4" s="7"/>
+      <c r="I4" s="7"/>
+      <c r="J4" s="7"/>
+      <c r="K4" s="7"/>
+      <c r="L4" s="8"/>
+    </row>
+    <row r="5" ht="13.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A5" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="9">
-        <f>[40]目录!H8</f>
-      </c>
-      <c r="C5" s="8" t="s">
+      <c r="B5" s="10"/>
+      <c r="C5" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="7">
-        <f>[40]目录!H9</f>
-      </c>
-      <c r="E5" s="10" t="s">
+      <c r="D5" s="8"/>
+      <c r="E5" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="F5" s="10"/>
-      <c r="G5" s="10"/>
-      <c r="H5" s="10"/>
-      <c r="I5" s="10"/>
-      <c r="J5" s="10"/>
-      <c r="K5" s="10"/>
-      <c r="L5" s="10"/>
-    </row>
-    <row r="6" ht="14.25" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A6" s="11" t="s">
+      <c r="F5" s="11"/>
+      <c r="G5" s="11"/>
+      <c r="H5" s="11"/>
+      <c r="I5" s="11"/>
+      <c r="J5" s="11"/>
+      <c r="K5" s="11"/>
+      <c r="L5" s="11"/>
+    </row>
+    <row r="6" ht="11.25" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A6" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="12" t="s">
+      <c r="B6" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="12"/>
-      <c r="D6" s="12"/>
-      <c r="E6" s="13" t="s">
+      <c r="C6" s="13"/>
+      <c r="D6" s="13"/>
+      <c r="E6" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="F6" s="13"/>
-      <c r="G6" s="13"/>
-      <c r="H6" s="13" t="s">
+      <c r="F6" s="14"/>
+      <c r="G6" s="14"/>
+      <c r="H6" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="I6" s="13"/>
-      <c r="J6" s="13"/>
-      <c r="K6" s="10" t="s">
+      <c r="I6" s="14"/>
+      <c r="J6" s="14"/>
+      <c r="K6" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="L6" s="10"/>
-    </row>
-    <row r="7" ht="14.25" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A7" s="11"/>
-      <c r="B7" s="12"/>
-      <c r="C7" s="12"/>
-      <c r="D7" s="12"/>
-      <c r="E7" s="14" t="s">
+      <c r="L6" s="11"/>
+    </row>
+    <row r="7" ht="11.25" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A7" s="12"/>
+      <c r="B7" s="13"/>
+      <c r="C7" s="13"/>
+      <c r="D7" s="13"/>
+      <c r="E7" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="F7" s="14"/>
-      <c r="G7" s="14"/>
-      <c r="H7" s="14" t="s">
+      <c r="F7" s="15"/>
+      <c r="G7" s="15"/>
+      <c r="H7" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="I7" s="14"/>
-      <c r="J7" s="14"/>
-      <c r="K7" s="10"/>
-      <c r="L7" s="10"/>
-      <c r="R7" s="15" t="s">
+      <c r="I7" s="15"/>
+      <c r="J7" s="15"/>
+      <c r="K7" s="11"/>
+      <c r="L7" s="11"/>
+      <c r="R7" s="16" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="8" ht="18" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B8" s="16" t="s">
+    <row r="8" ht="14.25" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B8" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="C8" s="16"/>
-      <c r="D8" s="16"/>
-      <c r="E8" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="F8" s="17" t="s">
+      <c r="C8" s="17"/>
+      <c r="D8" s="17"/>
+      <c r="E8" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="F8" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="G8" s="17" t="s">
+      <c r="G8" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="H8" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="I8" s="17" t="s">
+      <c r="H8" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="I8" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="J8" s="17" t="s">
+      <c r="J8" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="L8"/>
-      <c r="M8" s="18" t="s">
+      <c r="K8" s="4"/>
+      <c r="L8" s="4"/>
+      <c r="M8" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="N8" s="18"/>
-      <c r="O8" s="18"/>
-      <c r="P8" s="18"/>
-      <c r="R8" s="15"/>
-    </row>
-    <row r="9" ht="24.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A9" s="18" t="s">
+      <c r="N8" s="19"/>
+      <c r="O8" s="19"/>
+      <c r="P8" s="19"/>
+      <c r="R8" s="16"/>
+    </row>
+    <row r="9" ht="19.5" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A9" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="B9" s="19" t="s">
+      <c r="B9" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="C9" s="19"/>
-      <c r="D9" s="19"/>
-      <c r="L9"/>
-      <c r="N9" s="18" t="s">
+      <c r="C9" s="20"/>
+      <c r="D9" s="20"/>
+      <c r="K9" s="4"/>
+      <c r="L9" s="4"/>
+      <c r="N9" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="O9" s="18" t="s">
+      <c r="O9" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="P9" s="18" t="s">
+      <c r="P9" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="R9" s="15"/>
-    </row>
-    <row r="10" ht="24.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A10" s="18" t="s">
+      <c r="R9" s="16"/>
+    </row>
+    <row r="10" ht="19.5" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A10" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="B10" s="19" t="s">
+      <c r="B10" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="C10" s="19"/>
-      <c r="D10" s="19"/>
-      <c r="L10"/>
-      <c r="M10" s="18" t="s">
-        <v>20</v>
-      </c>
-      <c r="N10" s="18" t="s">
+      <c r="C10" s="20"/>
+      <c r="D10" s="20"/>
+      <c r="K10" s="4"/>
+      <c r="L10" s="4"/>
+      <c r="M10" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="N10" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="O10" s="18">
+      <c r="O10" s="19">
         <f>COUNTIF(H9:H103,"√")</f>
       </c>
-      <c r="P10" s="18">
+      <c r="P10" s="19">
         <f>O10/Q12</f>
       </c>
-      <c r="R10" s="15"/>
-    </row>
-    <row r="11" ht="24.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A11" s="18" t="s">
+      <c r="R10" s="16"/>
+    </row>
+    <row r="11" ht="19.5" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A11" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="B11" s="19" t="s">
+      <c r="B11" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="C11" s="19"/>
-      <c r="D11" s="19"/>
-      <c r="L11"/>
-      <c r="M11" s="18"/>
-      <c r="N11" s="18" t="s">
+      <c r="C11" s="20"/>
+      <c r="D11" s="20"/>
+      <c r="K11" s="4"/>
+      <c r="L11" s="4"/>
+      <c r="M11" s="19"/>
+      <c r="N11" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="O11" s="18">
+      <c r="O11" s="19">
         <f>COUNTIF(H9:H103,"×")</f>
       </c>
-      <c r="P11" s="18">
+      <c r="P11" s="19">
         <f>O11/Q12</f>
       </c>
-      <c r="Q11" s="18" t="s">
+      <c r="Q11" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="R11" s="15"/>
-    </row>
-    <row r="12" ht="24.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A12" s="18" t="s">
+      <c r="R11" s="16"/>
+    </row>
+    <row r="12" ht="19.5" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A12" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="B12" s="20" t="s">
+      <c r="B12" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="C12" s="20"/>
-      <c r="D12" s="20"/>
-      <c r="L12"/>
-      <c r="M12" s="18"/>
-      <c r="N12" s="18" t="s">
+      <c r="C12" s="21"/>
+      <c r="D12" s="21"/>
+      <c r="K12" s="4"/>
+      <c r="L12" s="4"/>
+      <c r="M12" s="19"/>
+      <c r="N12" s="19" t="s">
         <v>38</v>
       </c>
-      <c r="O12" s="18">
+      <c r="O12" s="19">
         <f>COUNTIF(H9:H103,"无")</f>
       </c>
-      <c r="P12" s="18">
+      <c r="P12" s="19">
         <f>O12/Q12</f>
       </c>
-      <c r="Q12" s="18">
+      <c r="Q12" s="19">
         <f>SUM(O10:O12)</f>
       </c>
-      <c r="R12" s="15"/>
-    </row>
-    <row r="13" ht="24.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A13" s="18" t="s">
+      <c r="R12" s="16"/>
+    </row>
+    <row r="13" ht="19.5" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A13" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="B13" s="19" t="s">
+      <c r="B13" s="20" t="s">
         <v>40</v>
       </c>
-      <c r="C13" s="19"/>
-      <c r="D13" s="19"/>
-      <c r="L13"/>
-      <c r="M13" s="18" t="s">
+      <c r="C13" s="20"/>
+      <c r="D13" s="20"/>
+      <c r="K13" s="4"/>
+      <c r="L13" s="4"/>
+      <c r="M13" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="N13" s="18" t="s">
+      <c r="N13" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="O13" s="18">
+      <c r="O13" s="19">
         <f>COUNTIF(I9:I103,"√")</f>
       </c>
-      <c r="P13" s="18">
+      <c r="P13" s="19">
         <f>O13/Q15</f>
       </c>
-      <c r="R13" s="15"/>
-    </row>
-    <row r="14" ht="24.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A14" s="18" t="s">
+      <c r="R13" s="16"/>
+    </row>
+    <row r="14" ht="19.5" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A14" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="B14" s="19" t="s">
+      <c r="B14" s="20" t="s">
         <v>42</v>
       </c>
-      <c r="C14" s="19"/>
-      <c r="D14" s="19"/>
-      <c r="L14"/>
-      <c r="M14" s="18"/>
-      <c r="N14" s="18" t="s">
+      <c r="C14" s="20"/>
+      <c r="D14" s="20"/>
+      <c r="K14" s="4"/>
+      <c r="L14" s="4"/>
+      <c r="M14" s="19"/>
+      <c r="N14" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="O14" s="18">
+      <c r="O14" s="19">
         <f>COUNTIF(I9:I103,"×")</f>
       </c>
-      <c r="P14" s="18">
+      <c r="P14" s="19">
         <f>O14/Q15</f>
       </c>
-      <c r="Q14" s="18" t="s">
+      <c r="Q14" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="R14" s="15"/>
-    </row>
-    <row r="15" ht="24.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A15" s="18" t="s">
+      <c r="R14" s="16"/>
+    </row>
+    <row r="15" ht="19.5" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A15" s="19" t="s">
         <v>43</v>
       </c>
-      <c r="B15" s="20" t="s">
+      <c r="B15" s="21" t="s">
         <v>44</v>
       </c>
-      <c r="C15" s="20"/>
-      <c r="D15" s="20"/>
-      <c r="L15"/>
-      <c r="M15" s="18"/>
-      <c r="N15" s="18" t="s">
+      <c r="C15" s="21"/>
+      <c r="D15" s="21"/>
+      <c r="K15" s="4"/>
+      <c r="L15" s="4"/>
+      <c r="M15" s="19"/>
+      <c r="N15" s="19" t="s">
         <v>38</v>
       </c>
-      <c r="O15" s="18">
+      <c r="O15" s="19">
         <f>COUNTIF(I9:I103,"无")</f>
       </c>
-      <c r="P15" s="18">
+      <c r="P15" s="19">
         <f>O15/Q15</f>
       </c>
-      <c r="Q15" s="18">
+      <c r="Q15" s="19">
         <f>SUM(O13:O15)</f>
       </c>
-      <c r="R15" s="15"/>
-    </row>
-    <row r="16" ht="24.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A16" s="18" t="s">
+      <c r="R15" s="16"/>
+    </row>
+    <row r="16" ht="19.5" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A16" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="B16" s="19" t="s">
+      <c r="B16" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="C16" s="19"/>
-      <c r="D16" s="19"/>
-      <c r="L16"/>
-      <c r="M16" s="18" t="s">
+      <c r="C16" s="20"/>
+      <c r="D16" s="20"/>
+      <c r="K16" s="4"/>
+      <c r="L16" s="4"/>
+      <c r="M16" s="19" t="s">
         <v>47</v>
       </c>
-      <c r="N16" s="18"/>
-      <c r="O16" s="18"/>
-      <c r="P16" s="18"/>
-      <c r="R16" s="15"/>
-    </row>
-    <row r="17" ht="24.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A17" s="18" t="s">
+      <c r="N16" s="19"/>
+      <c r="O16" s="19"/>
+      <c r="P16" s="19"/>
+      <c r="R16" s="16"/>
+    </row>
+    <row r="17" ht="19.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A17" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="B17" s="9" t="s">
+      <c r="B17" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="C17" s="9"/>
-      <c r="D17" s="9"/>
-      <c r="L17"/>
-      <c r="M17" s="18" t="s">
-        <v>20</v>
-      </c>
-      <c r="N17" s="18" t="s">
+      <c r="C17" s="10"/>
+      <c r="D17" s="10"/>
+      <c r="K17" s="4"/>
+      <c r="L17" s="4"/>
+      <c r="M17" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="N17" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="O17" s="18">
+      <c r="O17" s="19">
         <f>COUNTIF(E5:E75,"√")</f>
       </c>
     </row>
-    <row r="18" ht="24.75" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A18" s="18" t="s">
+    <row r="18" ht="19.5" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A18" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="B18" s="19" t="s">
+      <c r="B18" s="20" t="s">
         <v>51</v>
       </c>
-      <c r="C18" s="19"/>
-      <c r="D18" s="19"/>
-      <c r="L18"/>
-      <c r="M18" s="18"/>
-      <c r="N18" s="18" t="s">
+      <c r="C18" s="20"/>
+      <c r="D18" s="20"/>
+      <c r="K18" s="4"/>
+      <c r="L18" s="4"/>
+      <c r="M18" s="19"/>
+      <c r="N18" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="O18" s="18">
+      <c r="O18" s="19">
         <f>COUNTIF(E5:E75,"×")</f>
       </c>
-      <c r="Q18" s="18" t="s">
+      <c r="Q18" s="19" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="19" ht="24.75" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A19" s="18" t="s">
+    <row r="19" ht="19.5" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A19" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="B19" s="19" t="s">
+      <c r="B19" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="C19" s="19"/>
-      <c r="D19" s="19"/>
-      <c r="L19"/>
-      <c r="M19" s="18"/>
-      <c r="N19" s="18" t="s">
+      <c r="C19" s="20"/>
+      <c r="D19" s="20"/>
+      <c r="K19" s="4"/>
+      <c r="L19" s="4"/>
+      <c r="M19" s="19"/>
+      <c r="N19" s="19" t="s">
         <v>38</v>
       </c>
-      <c r="O19" s="18">
+      <c r="O19" s="19">
         <f>COUNTIF(E5:E75,"无")</f>
       </c>
-      <c r="Q19" s="18">
+      <c r="Q19" s="19">
         <f>SUM(O17:O19)</f>
       </c>
     </row>
-    <row r="20" ht="24.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A20" s="18" t="s">
+    <row r="20" ht="19.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A20" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="B20" s="19" t="s">
+      <c r="B20" s="20" t="s">
         <v>55</v>
       </c>
-      <c r="C20" s="19"/>
-      <c r="D20" s="19"/>
-      <c r="L20"/>
-      <c r="M20" s="18" t="s">
+      <c r="C20" s="20"/>
+      <c r="D20" s="20"/>
+      <c r="K20" s="4"/>
+      <c r="L20" s="4"/>
+      <c r="M20" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="N20" s="18" t="s">
+      <c r="N20" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="O20" s="18">
+      <c r="O20" s="19">
         <f>COUNTIF(F5:F75,"√")</f>
       </c>
     </row>
-    <row r="21" ht="24.75" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A21" s="18" t="s">
+    <row r="21" ht="19.5" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A21" s="19" t="s">
         <v>56</v>
       </c>
-      <c r="B21" s="19" t="s">
+      <c r="B21" s="20" t="s">
         <v>57</v>
       </c>
-      <c r="C21" s="19"/>
-      <c r="D21" s="19"/>
-      <c r="L21"/>
-      <c r="M21" s="18"/>
-      <c r="N21" s="18" t="s">
+      <c r="C21" s="20"/>
+      <c r="D21" s="20"/>
+      <c r="K21" s="4"/>
+      <c r="L21" s="4"/>
+      <c r="M21" s="19"/>
+      <c r="N21" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="O21" s="18">
+      <c r="O21" s="19">
         <f>COUNTIF(F5:F75,"×")</f>
       </c>
-      <c r="Q21" s="18" t="s">
+      <c r="Q21" s="19" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="22" ht="24.75" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A22" s="18" t="s">
+    <row r="22" ht="19.5" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A22" s="19" t="s">
         <v>58</v>
       </c>
-      <c r="B22" s="19" t="s">
+      <c r="B22" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="C22" s="19"/>
-      <c r="D22" s="19"/>
-      <c r="L22"/>
-      <c r="M22" s="18"/>
-      <c r="N22" s="18" t="s">
+      <c r="C22" s="20"/>
+      <c r="D22" s="20"/>
+      <c r="K22" s="4"/>
+      <c r="L22" s="4"/>
+      <c r="M22" s="19"/>
+      <c r="N22" s="19" t="s">
         <v>38</v>
       </c>
-      <c r="O22" s="18">
+      <c r="O22" s="19">
         <f>COUNTIF(F5:F75,"无")</f>
       </c>
-      <c r="Q22" s="18">
+      <c r="Q22" s="19">
         <f>SUM(O20:O22)</f>
       </c>
     </row>
-    <row r="23" ht="24.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A23" s="18" t="s">
+    <row r="23" ht="19.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A23" s="19" t="s">
         <v>60</v>
       </c>
-      <c r="B23" s="20" t="s">
+      <c r="B23" s="21" t="s">
         <v>61</v>
       </c>
-      <c r="C23" s="20"/>
-      <c r="D23" s="20"/>
-      <c r="L23"/>
-    </row>
-    <row r="24" ht="24.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A24" s="18" t="s">
+      <c r="C23" s="21"/>
+      <c r="D23" s="21"/>
+      <c r="K23" s="4"/>
+      <c r="L23" s="4"/>
+    </row>
+    <row r="24" ht="19.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A24" s="19" t="s">
         <v>62</v>
       </c>
-      <c r="B24" s="20" t="s">
+      <c r="B24" s="21" t="s">
         <v>63</v>
       </c>
-      <c r="C24" s="20"/>
-      <c r="D24" s="20"/>
-      <c r="L24"/>
-    </row>
-    <row r="25" ht="24.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A25" s="18" t="s">
+      <c r="C24" s="21"/>
+      <c r="D24" s="21"/>
+      <c r="K24" s="4"/>
+      <c r="L24" s="4"/>
+    </row>
+    <row r="25" ht="19.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A25" s="19" t="s">
         <v>64</v>
       </c>
-      <c r="B25" s="20" t="s">
+      <c r="B25" s="21" t="s">
         <v>65</v>
       </c>
-      <c r="C25" s="20"/>
-      <c r="D25" s="20"/>
-      <c r="L25"/>
-    </row>
-    <row r="26" ht="24.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A26" s="18" t="s">
+      <c r="C25" s="21"/>
+      <c r="D25" s="21"/>
+      <c r="K25" s="4"/>
+      <c r="L25" s="4"/>
+    </row>
+    <row r="26" ht="19.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A26" s="19" t="s">
         <v>66</v>
       </c>
-      <c r="B26" s="20" t="s">
+      <c r="B26" s="21" t="s">
         <v>67</v>
       </c>
-      <c r="C26" s="20"/>
-      <c r="D26" s="20"/>
-      <c r="L26"/>
-    </row>
-    <row r="27" ht="24.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A27" s="18" t="s">
+      <c r="C26" s="21"/>
+      <c r="D26" s="21"/>
+      <c r="K26" s="4"/>
+      <c r="L26" s="4"/>
+    </row>
+    <row r="27" ht="19.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A27" s="19" t="s">
         <v>68</v>
       </c>
-      <c r="B27" s="20" t="s">
+      <c r="B27" s="21" t="s">
         <v>69</v>
       </c>
-      <c r="C27" s="20"/>
-      <c r="D27" s="20"/>
-      <c r="L27"/>
-    </row>
-    <row r="28" ht="24.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A28" s="18" t="s">
+      <c r="C27" s="21"/>
+      <c r="D27" s="21"/>
+      <c r="K27" s="4"/>
+      <c r="L27" s="4"/>
+    </row>
+    <row r="28" ht="19.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A28" s="19" t="s">
         <v>70</v>
       </c>
-      <c r="B28" s="19" t="s">
+      <c r="B28" s="20" t="s">
         <v>71</v>
       </c>
-      <c r="C28" s="19"/>
-      <c r="D28" s="19"/>
-      <c r="L28"/>
-    </row>
-    <row r="29" ht="24.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A29" s="18" t="s">
+      <c r="C28" s="20"/>
+      <c r="D28" s="20"/>
+      <c r="K28" s="4"/>
+      <c r="L28" s="4"/>
+    </row>
+    <row r="29" ht="19.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A29" s="19" t="s">
         <v>72</v>
       </c>
-      <c r="B29" s="20" t="s">
+      <c r="B29" s="21" t="s">
         <v>73</v>
       </c>
-      <c r="C29" s="20"/>
-      <c r="D29" s="20"/>
-      <c r="L29"/>
-    </row>
-    <row r="30" ht="24.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A30" s="18" t="s">
+      <c r="C29" s="21"/>
+      <c r="D29" s="21"/>
+      <c r="K29" s="4"/>
+      <c r="L29" s="4"/>
+    </row>
+    <row r="30" ht="19.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A30" s="19" t="s">
         <v>74</v>
       </c>
-      <c r="B30" s="20" t="s">
+      <c r="B30" s="21" t="s">
         <v>75</v>
       </c>
-      <c r="C30" s="20"/>
-      <c r="D30" s="20"/>
-      <c r="L30"/>
-    </row>
-    <row r="31" ht="24.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A31" s="18" t="s">
+      <c r="C30" s="21"/>
+      <c r="D30" s="21"/>
+      <c r="K30" s="4"/>
+      <c r="L30" s="4"/>
+    </row>
+    <row r="31" ht="19.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A31" s="19" t="s">
         <v>76</v>
       </c>
-      <c r="B31" s="20" t="s">
+      <c r="B31" s="21" t="s">
         <v>77</v>
       </c>
-      <c r="C31" s="20"/>
-      <c r="D31" s="20"/>
-      <c r="L31"/>
-    </row>
-    <row r="32" ht="24.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A32" s="18" t="s">
+      <c r="C31" s="21"/>
+      <c r="D31" s="21"/>
+      <c r="K31" s="4"/>
+      <c r="L31" s="4"/>
+    </row>
+    <row r="32" ht="19.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A32" s="19" t="s">
         <v>78</v>
       </c>
-      <c r="B32" s="20" t="s">
+      <c r="B32" s="21" t="s">
         <v>79</v>
       </c>
-      <c r="C32" s="20"/>
-      <c r="D32" s="20"/>
-      <c r="L32"/>
-    </row>
-    <row r="33" ht="24.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A33" s="18" t="s">
+      <c r="C32" s="21"/>
+      <c r="D32" s="21"/>
+      <c r="K32" s="4"/>
+      <c r="L32" s="4"/>
+    </row>
+    <row r="33" ht="19.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A33" s="19" t="s">
         <v>80</v>
       </c>
-      <c r="B33" s="20" t="s">
+      <c r="B33" s="21" t="s">
         <v>81</v>
       </c>
-      <c r="C33" s="20"/>
-      <c r="D33" s="20"/>
-      <c r="L33"/>
-    </row>
-    <row r="34" ht="24.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A34" s="18" t="s">
+      <c r="C33" s="21"/>
+      <c r="D33" s="21"/>
+      <c r="K33" s="4"/>
+      <c r="L33" s="4"/>
+    </row>
+    <row r="34" ht="19.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A34" s="19" t="s">
         <v>82</v>
       </c>
-      <c r="B34" s="19" t="s">
+      <c r="B34" s="20" t="s">
         <v>83</v>
       </c>
-      <c r="C34" s="19"/>
-      <c r="D34" s="19"/>
-      <c r="L34"/>
-    </row>
-    <row r="35" ht="24.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A35" s="18" t="s">
+      <c r="C34" s="20"/>
+      <c r="D34" s="20"/>
+      <c r="K34" s="4"/>
+      <c r="L34" s="4"/>
+    </row>
+    <row r="35" ht="19.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A35" s="19" t="s">
         <v>84</v>
       </c>
-      <c r="B35" s="20" t="s">
+      <c r="B35" s="21" t="s">
         <v>85</v>
       </c>
-      <c r="C35" s="20"/>
-      <c r="D35" s="20"/>
-      <c r="L35"/>
-    </row>
-    <row r="36" ht="24.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A36" s="18" t="s">
+      <c r="C35" s="21"/>
+      <c r="D35" s="21"/>
+      <c r="K35" s="4"/>
+      <c r="L35" s="4"/>
+    </row>
+    <row r="36" ht="19.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A36" s="19" t="s">
         <v>86</v>
       </c>
-      <c r="B36" s="20" t="s">
+      <c r="B36" s="21" t="s">
         <v>87</v>
       </c>
-      <c r="C36" s="20"/>
-      <c r="D36" s="20"/>
-      <c r="L36"/>
-    </row>
-    <row r="37" ht="24.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A37" s="18" t="s">
+      <c r="C36" s="21"/>
+      <c r="D36" s="21"/>
+      <c r="K36" s="4"/>
+      <c r="L36" s="4"/>
+    </row>
+    <row r="37" ht="19.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A37" s="19" t="s">
         <v>88</v>
       </c>
-      <c r="B37" s="20" t="s">
+      <c r="B37" s="21" t="s">
         <v>89</v>
       </c>
-      <c r="C37" s="20"/>
-      <c r="D37" s="20"/>
-      <c r="L37"/>
-    </row>
-    <row r="38" ht="24.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A38" s="18" t="s">
+      <c r="C37" s="21"/>
+      <c r="D37" s="21"/>
+      <c r="K37" s="4"/>
+      <c r="L37" s="4"/>
+    </row>
+    <row r="38" ht="19.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A38" s="19" t="s">
         <v>90</v>
       </c>
-      <c r="B38" s="21" t="s">
+      <c r="B38" s="22" t="s">
         <v>91</v>
       </c>
-      <c r="C38" s="21"/>
-      <c r="D38" s="21"/>
-      <c r="K38" s="22" t="s">
+      <c r="C38" s="22"/>
+      <c r="D38" s="22"/>
+      <c r="K38" s="23" t="s">
         <v>92</v>
       </c>
-      <c r="L38" s="22"/>
-    </row>
-    <row r="39" ht="24.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A39" s="18" t="s">
+      <c r="L38" s="23"/>
+    </row>
+    <row r="39" ht="19.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A39" s="19" t="s">
         <v>93</v>
       </c>
-      <c r="B39" s="21" t="s">
+      <c r="B39" s="22" t="s">
         <v>94</v>
       </c>
-      <c r="C39" s="21"/>
-      <c r="D39" s="21"/>
-      <c r="K39" s="22" t="s">
+      <c r="C39" s="22"/>
+      <c r="D39" s="22"/>
+      <c r="K39" s="23" t="s">
         <v>92</v>
       </c>
-      <c r="L39" s="22"/>
-    </row>
-    <row r="40" ht="24.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A40" s="18" t="s">
+      <c r="L39" s="23"/>
+    </row>
+    <row r="40" ht="19.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A40" s="19" t="s">
         <v>95</v>
       </c>
-      <c r="B40" s="21" t="s">
+      <c r="B40" s="22" t="s">
         <v>96</v>
       </c>
-      <c r="C40" s="21"/>
-      <c r="D40" s="21"/>
-      <c r="K40" s="22" t="s">
+      <c r="C40" s="22"/>
+      <c r="D40" s="22"/>
+      <c r="K40" s="23" t="s">
         <v>92</v>
       </c>
-      <c r="L40" s="22"/>
-    </row>
-    <row r="41" ht="24.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A41" s="18" t="s">
+      <c r="L40" s="23"/>
+    </row>
+    <row r="41" ht="19.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A41" s="19" t="s">
         <v>97</v>
       </c>
-      <c r="B41" s="20" t="s">
+      <c r="B41" s="21" t="s">
         <v>98</v>
       </c>
-      <c r="C41" s="20"/>
-      <c r="D41" s="20"/>
-      <c r="L41"/>
-    </row>
-    <row r="42" ht="24.75" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A42" s="18" t="s">
+      <c r="C41" s="21"/>
+      <c r="D41" s="21"/>
+      <c r="K41" s="4"/>
+      <c r="L41" s="4"/>
+    </row>
+    <row r="42" ht="19.5" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A42" s="19" t="s">
         <v>99</v>
       </c>
-      <c r="B42" s="20" t="s">
+      <c r="B42" s="21" t="s">
         <v>63</v>
       </c>
-      <c r="C42" s="20"/>
-      <c r="D42" s="20"/>
-    </row>
-    <row r="43" ht="24.75" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A43" s="18" t="s">
+      <c r="C42" s="21"/>
+      <c r="D42" s="21"/>
+    </row>
+    <row r="43" ht="19.5" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A43" s="19" t="s">
         <v>100</v>
       </c>
-      <c r="B43" s="20" t="s">
+      <c r="B43" s="21" t="s">
         <v>61</v>
       </c>
-      <c r="C43" s="20"/>
-      <c r="D43" s="20"/>
-    </row>
-    <row r="44" ht="24.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A44" s="18" t="s">
+      <c r="C43" s="21"/>
+      <c r="D43" s="21"/>
+    </row>
+    <row r="44" ht="19.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A44" s="19" t="s">
         <v>101</v>
       </c>
-      <c r="B44" s="20" t="s">
+      <c r="B44" s="21" t="s">
         <v>102</v>
       </c>
-      <c r="C44" s="20"/>
-      <c r="D44" s="20"/>
-      <c r="K44" s="22" t="s">
+      <c r="C44" s="21"/>
+      <c r="D44" s="21"/>
+      <c r="K44" s="23" t="s">
         <v>92</v>
       </c>
-      <c r="L44" s="22"/>
-    </row>
-    <row r="45" ht="24.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A45" s="18" t="s">
+      <c r="L44" s="23"/>
+    </row>
+    <row r="45" ht="19.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A45" s="19" t="s">
         <v>103</v>
       </c>
-      <c r="B45" s="20" t="s">
+      <c r="B45" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="C45" s="20"/>
-      <c r="D45" s="20"/>
-      <c r="K45" s="22" t="s">
+      <c r="C45" s="21"/>
+      <c r="D45" s="21"/>
+      <c r="K45" s="23" t="s">
         <v>92</v>
       </c>
-      <c r="L45" s="22"/>
-    </row>
-    <row r="46" ht="24.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A46" s="18" t="s">
+      <c r="L45" s="23"/>
+    </row>
+    <row r="46" ht="19.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A46" s="19" t="s">
         <v>105</v>
       </c>
-      <c r="B46" s="20" t="s">
+      <c r="B46" s="21" t="s">
         <v>106</v>
       </c>
-      <c r="C46" s="20"/>
-      <c r="D46" s="20"/>
-      <c r="K46" s="22" t="s">
+      <c r="C46" s="21"/>
+      <c r="D46" s="21"/>
+      <c r="K46" s="23" t="s">
         <v>92</v>
       </c>
-      <c r="L46" s="22"/>
-    </row>
-    <row r="47" ht="24.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B47" s="23" t="s">
+      <c r="L46" s="23"/>
+    </row>
+    <row r="47" ht="19.5" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B47" s="24" t="s">
         <v>107</v>
       </c>
-      <c r="C47" s="23"/>
-      <c r="D47" s="23"/>
-      <c r="E47" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="F47" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="G47" s="17" t="s">
+      <c r="C47" s="24"/>
+      <c r="D47" s="24"/>
+      <c r="E47" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="F47" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="G47" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="H47" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="I47" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="J47" s="17" t="s">
+      <c r="H47" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="I47" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="J47" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="L47"/>
-    </row>
-    <row r="48" ht="24.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A48" s="18" t="s">
+      <c r="K47" s="4"/>
+      <c r="L47" s="4"/>
+    </row>
+    <row r="48" ht="19.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A48" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="B48" s="20" t="s">
+      <c r="B48" s="21" t="s">
         <v>108</v>
       </c>
-      <c r="C48" s="20"/>
-      <c r="D48" s="20"/>
-      <c r="L48"/>
-    </row>
-    <row r="49" ht="24.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A49" s="18" t="s">
+      <c r="C48" s="21"/>
+      <c r="D48" s="21"/>
+      <c r="K48" s="4"/>
+      <c r="L48" s="4"/>
+    </row>
+    <row r="49" ht="19.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A49" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="B49" s="19" t="s">
+      <c r="B49" s="20" t="s">
         <v>109</v>
       </c>
-      <c r="C49" s="19"/>
-      <c r="D49" s="19"/>
-      <c r="L49"/>
-    </row>
-    <row r="50" ht="24.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A50" s="18" t="s">
+      <c r="C49" s="20"/>
+      <c r="D49" s="20"/>
+      <c r="K49" s="4"/>
+      <c r="L49" s="4"/>
+    </row>
+    <row r="50" ht="19.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A50" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="B50" s="19" t="s">
+      <c r="B50" s="20" t="s">
         <v>110</v>
       </c>
-      <c r="C50" s="19"/>
-      <c r="D50" s="19"/>
-      <c r="L50"/>
-    </row>
-    <row r="51" ht="24.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B51" s="23" t="s">
+      <c r="C50" s="20"/>
+      <c r="D50" s="20"/>
+      <c r="K50" s="4"/>
+      <c r="L50" s="4"/>
+    </row>
+    <row r="51" ht="19.5" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B51" s="24" t="s">
         <v>111</v>
       </c>
-      <c r="C51" s="23"/>
-      <c r="D51" s="23"/>
-      <c r="E51" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="F51" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="G51" s="17" t="s">
+      <c r="C51" s="24"/>
+      <c r="D51" s="24"/>
+      <c r="E51" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="F51" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="G51" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="H51" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="I51" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="J51" s="17" t="s">
+      <c r="H51" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="I51" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="J51" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="L51"/>
-    </row>
-    <row r="52" ht="24.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A52" s="18" t="s">
+      <c r="K51" s="4"/>
+      <c r="L51" s="4"/>
+    </row>
+    <row r="52" ht="19.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A52" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="B52" s="20" t="s">
+      <c r="B52" s="21" t="s">
         <v>112</v>
       </c>
-      <c r="C52" s="20"/>
-      <c r="D52" s="20"/>
-      <c r="L52"/>
-    </row>
-    <row r="53" ht="24.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A53" s="18" t="s">
+      <c r="C52" s="21"/>
+      <c r="D52" s="21"/>
+      <c r="K52" s="4"/>
+      <c r="L52" s="4"/>
+    </row>
+    <row r="53" ht="19.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A53" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="B53" s="24" t="s">
+      <c r="B53" s="25" t="s">
         <v>113</v>
       </c>
-      <c r="C53" s="24"/>
-      <c r="D53" s="24"/>
-      <c r="K53" s="22" t="s">
+      <c r="C53" s="25"/>
+      <c r="D53" s="25"/>
+      <c r="K53" s="23" t="s">
         <v>92</v>
       </c>
-      <c r="L53" s="22"/>
-    </row>
-    <row r="54" ht="24.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B54" s="23" t="s">
+      <c r="L53" s="23"/>
+    </row>
+    <row r="54" ht="19.5" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B54" s="24" t="s">
         <v>114</v>
       </c>
-      <c r="C54" s="23"/>
-      <c r="D54" s="23"/>
-      <c r="E54" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="F54" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="G54" s="17" t="s">
+      <c r="C54" s="24"/>
+      <c r="D54" s="24"/>
+      <c r="E54" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="F54" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="G54" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="H54" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="I54" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="J54" s="17" t="s">
+      <c r="H54" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="I54" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="J54" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="L54"/>
-    </row>
-    <row r="55" ht="24.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A55" s="18" t="s">
+      <c r="K54" s="4"/>
+      <c r="L54" s="4"/>
+    </row>
+    <row r="55" ht="19.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A55" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="B55" s="25" t="s">
+      <c r="B55" s="26" t="s">
         <v>115</v>
       </c>
-      <c r="C55" s="25"/>
-      <c r="D55" s="25"/>
-      <c r="L55"/>
-    </row>
-    <row r="56" ht="24.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A56" s="18" t="s">
+      <c r="C55" s="26"/>
+      <c r="D55" s="26"/>
+      <c r="K55" s="4"/>
+      <c r="L55" s="4"/>
+    </row>
+    <row r="56" ht="19.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A56" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="B56" s="25" t="s">
+      <c r="B56" s="26" t="s">
         <v>116</v>
       </c>
-      <c r="C56" s="25"/>
-      <c r="D56" s="25"/>
-      <c r="L56"/>
-    </row>
-    <row r="57" ht="24.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A57" s="18" t="s">
+      <c r="C56" s="26"/>
+      <c r="D56" s="26"/>
+      <c r="K56" s="4"/>
+      <c r="L56" s="4"/>
+    </row>
+    <row r="57" ht="19.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A57" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="B57" s="20" t="s">
+      <c r="B57" s="21" t="s">
         <v>117</v>
       </c>
-      <c r="C57" s="20"/>
-      <c r="D57" s="20"/>
-      <c r="L57"/>
-    </row>
-    <row r="58" ht="24.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A58" s="18" t="s">
+      <c r="C57" s="21"/>
+      <c r="D57" s="21"/>
+      <c r="K57" s="4"/>
+      <c r="L57" s="4"/>
+    </row>
+    <row r="58" ht="19.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A58" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="B58" s="20" t="s">
+      <c r="B58" s="21" t="s">
         <v>118</v>
       </c>
-      <c r="C58" s="20"/>
-      <c r="D58" s="20"/>
-      <c r="L58"/>
-    </row>
-    <row r="59" ht="24.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A59" s="18" t="s">
+      <c r="C58" s="21"/>
+      <c r="D58" s="21"/>
+      <c r="K58" s="4"/>
+      <c r="L58" s="4"/>
+    </row>
+    <row r="59" ht="19.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A59" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="B59" s="20" t="s">
+      <c r="B59" s="21" t="s">
         <v>119</v>
       </c>
-      <c r="C59" s="20"/>
-      <c r="D59" s="20"/>
-      <c r="L59"/>
-    </row>
-    <row r="60" ht="24.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B60" s="23" t="s">
+      <c r="C59" s="21"/>
+      <c r="D59" s="21"/>
+      <c r="K59" s="4"/>
+      <c r="L59" s="4"/>
+    </row>
+    <row r="60" ht="19.5" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B60" s="24" t="s">
         <v>120</v>
       </c>
-      <c r="C60" s="23"/>
-      <c r="D60" s="23"/>
-      <c r="E60" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="F60" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="G60" s="17" t="s">
+      <c r="C60" s="24"/>
+      <c r="D60" s="24"/>
+      <c r="E60" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="F60" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="G60" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="H60" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="I60" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="J60" s="17" t="s">
+      <c r="H60" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="I60" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="J60" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="L60"/>
-    </row>
-    <row r="61" ht="24.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A61" s="18" t="s">
+      <c r="K60" s="4"/>
+      <c r="L60" s="4"/>
+    </row>
+    <row r="61" ht="19.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A61" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="B61" s="20" t="s">
+      <c r="B61" s="21" t="s">
         <v>121</v>
       </c>
-      <c r="C61" s="20"/>
-      <c r="D61" s="20"/>
-      <c r="L61"/>
-    </row>
-    <row r="62" ht="24.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A62" s="18" t="s">
+      <c r="C61" s="21"/>
+      <c r="D61" s="21"/>
+      <c r="K61" s="4"/>
+      <c r="L61" s="4"/>
+    </row>
+    <row r="62" ht="19.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A62" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="B62" s="20" t="s">
+      <c r="B62" s="21" t="s">
         <v>122</v>
       </c>
-      <c r="C62" s="20"/>
-      <c r="D62" s="20"/>
-      <c r="L62"/>
-    </row>
-    <row r="63" ht="24.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A63" s="18" t="s">
+      <c r="C62" s="21"/>
+      <c r="D62" s="21"/>
+      <c r="K62" s="4"/>
+      <c r="L62" s="4"/>
+    </row>
+    <row r="63" ht="19.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A63" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="B63" s="20" t="s">
+      <c r="B63" s="21" t="s">
         <v>123</v>
       </c>
-      <c r="C63" s="20"/>
-      <c r="D63" s="20"/>
-      <c r="L63"/>
-    </row>
-    <row r="64" ht="24.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A64" s="18" t="s">
+      <c r="C63" s="21"/>
+      <c r="D63" s="21"/>
+      <c r="K63" s="4"/>
+      <c r="L63" s="4"/>
+    </row>
+    <row r="64" ht="19.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A64" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="B64" s="20" t="s">
+      <c r="B64" s="21" t="s">
         <v>124</v>
       </c>
-      <c r="C64" s="20"/>
-      <c r="D64" s="20"/>
-      <c r="L64"/>
-    </row>
-    <row r="65" ht="24.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A65" s="18" t="s">
+      <c r="C64" s="21"/>
+      <c r="D64" s="21"/>
+      <c r="K64" s="4"/>
+      <c r="L64" s="4"/>
+    </row>
+    <row r="65" ht="19.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A65" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="B65" s="19" t="s">
+      <c r="B65" s="20" t="s">
         <v>125</v>
       </c>
-      <c r="C65" s="19"/>
-      <c r="D65" s="19"/>
-      <c r="L65"/>
-    </row>
-    <row r="66" ht="24.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A66" s="18" t="s">
+      <c r="C65" s="20"/>
+      <c r="D65" s="20"/>
+      <c r="K65" s="4"/>
+      <c r="L65" s="4"/>
+    </row>
+    <row r="66" ht="19.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A66" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="B66" s="25" t="s">
+      <c r="B66" s="26" t="s">
         <v>126</v>
       </c>
-      <c r="C66" s="25"/>
-      <c r="D66" s="25"/>
-      <c r="L66"/>
-    </row>
-    <row r="67" ht="24.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A67" s="18" t="s">
+      <c r="C66" s="26"/>
+      <c r="D66" s="26"/>
+      <c r="K66" s="4"/>
+      <c r="L66" s="4"/>
+    </row>
+    <row r="67" ht="19.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A67" s="19" t="s">
         <v>43</v>
       </c>
-      <c r="B67" s="20" t="s">
+      <c r="B67" s="21" t="s">
         <v>127</v>
       </c>
-      <c r="C67" s="20"/>
-      <c r="D67" s="20"/>
-      <c r="E67" s="26" t="s">
-        <v>38</v>
-      </c>
-      <c r="F67" s="26" t="s">
-        <v>38</v>
-      </c>
-      <c r="H67" s="26" t="s">
-        <v>38</v>
-      </c>
-      <c r="I67" s="26" t="s">
-        <v>38</v>
-      </c>
-      <c r="L67"/>
-    </row>
-    <row r="68" ht="24.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A68" s="18" t="s">
+      <c r="C67" s="21"/>
+      <c r="D67" s="21"/>
+      <c r="E67" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="F67" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="H67" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="I67" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="K67" s="4"/>
+      <c r="L67" s="4"/>
+    </row>
+    <row r="68" ht="19.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A68" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="B68" s="20" t="s">
-        <v>128</v>
-      </c>
-      <c r="C68" s="20"/>
-      <c r="D68" s="20"/>
-      <c r="L68"/>
-    </row>
-    <row r="69" ht="24.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A69" s="18" t="s">
+      <c r="B68" s="21" t="s">
+        <v>129</v>
+      </c>
+      <c r="C68" s="21"/>
+      <c r="D68" s="21"/>
+      <c r="K68" s="4"/>
+      <c r="L68" s="4"/>
+    </row>
+    <row r="69" ht="19.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A69" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="B69" s="20" t="s">
-        <v>129</v>
-      </c>
-      <c r="C69" s="20"/>
-      <c r="D69" s="20"/>
-      <c r="L69"/>
-    </row>
-    <row r="70" ht="24.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A70" s="18" t="s">
+      <c r="B69" s="21" t="s">
+        <v>130</v>
+      </c>
+      <c r="C69" s="21"/>
+      <c r="D69" s="21"/>
+      <c r="K69" s="4"/>
+      <c r="L69" s="4"/>
+    </row>
+    <row r="70" ht="19.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A70" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="B70" s="20" t="s">
-        <v>130</v>
-      </c>
-      <c r="C70" s="20"/>
-      <c r="D70" s="20"/>
-      <c r="L70"/>
-    </row>
-    <row r="71" ht="24.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B71" s="23" t="s">
+      <c r="B70" s="21" t="s">
         <v>131</v>
       </c>
-      <c r="C71" s="23"/>
-      <c r="D71" s="23"/>
-      <c r="E71" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="F71" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="G71" s="17" t="s">
+      <c r="C70" s="21"/>
+      <c r="D70" s="21"/>
+      <c r="K70" s="4"/>
+      <c r="L70" s="4"/>
+    </row>
+    <row r="71" ht="19.5" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B71" s="24" t="s">
+        <v>132</v>
+      </c>
+      <c r="C71" s="24"/>
+      <c r="D71" s="24"/>
+      <c r="E71" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="F71" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="G71" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="H71" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="I71" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="J71" s="17" t="s">
+      <c r="H71" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="I71" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="J71" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="L71"/>
-    </row>
-    <row r="72" ht="24.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A72" s="18" t="s">
+      <c r="K71" s="4"/>
+      <c r="L71" s="4"/>
+    </row>
+    <row r="72" ht="19.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A72" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="B72" s="19" t="s">
-        <v>132</v>
-      </c>
-      <c r="C72" s="19"/>
-      <c r="D72" s="19"/>
-      <c r="L72"/>
-    </row>
-    <row r="73" ht="24.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A73" s="18" t="s">
+      <c r="B72" s="20" t="s">
+        <v>133</v>
+      </c>
+      <c r="C72" s="20"/>
+      <c r="D72" s="20"/>
+      <c r="K72" s="4"/>
+      <c r="L72" s="4"/>
+    </row>
+    <row r="73" ht="19.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A73" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="B73" s="19" t="s">
-        <v>133</v>
-      </c>
-      <c r="C73" s="19"/>
-      <c r="D73" s="19"/>
-      <c r="L73"/>
-    </row>
-    <row r="74" ht="24.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A74" s="18" t="s">
+      <c r="B73" s="20" t="s">
+        <v>134</v>
+      </c>
+      <c r="C73" s="20"/>
+      <c r="D73" s="20"/>
+      <c r="K73" s="4"/>
+      <c r="L73" s="4"/>
+    </row>
+    <row r="74" ht="19.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A74" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="B74" s="19" t="s">
-        <v>134</v>
-      </c>
-      <c r="C74" s="19"/>
-      <c r="D74" s="19"/>
-      <c r="L74"/>
-    </row>
-    <row r="75" ht="24.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A75" s="18" t="s">
+      <c r="B74" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="C74" s="20"/>
+      <c r="D74" s="20"/>
+      <c r="K74" s="4"/>
+      <c r="L74" s="4"/>
+    </row>
+    <row r="75" ht="19.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A75" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="B75" s="19" t="s">
-        <v>135</v>
-      </c>
-      <c r="C75" s="19"/>
-      <c r="D75" s="19"/>
-      <c r="L75"/>
-    </row>
-    <row r="76" ht="24.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A76" s="18" t="s">
+      <c r="B75" s="20" t="s">
+        <v>136</v>
+      </c>
+      <c r="C75" s="20"/>
+      <c r="D75" s="20"/>
+      <c r="K75" s="4"/>
+      <c r="L75" s="4"/>
+    </row>
+    <row r="76" ht="19.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A76" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="B76" s="20" t="s">
-        <v>136</v>
-      </c>
-      <c r="C76" s="20"/>
-      <c r="D76" s="20"/>
-      <c r="L76"/>
-    </row>
-    <row r="77" ht="24.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A77" s="18" t="s">
+      <c r="B76" s="21" t="s">
+        <v>137</v>
+      </c>
+      <c r="C76" s="21"/>
+      <c r="D76" s="21"/>
+      <c r="K76" s="4"/>
+      <c r="L76" s="4"/>
+    </row>
+    <row r="77" ht="19.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A77" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="B77" s="19" t="s">
-        <v>137</v>
-      </c>
-      <c r="C77" s="19"/>
-      <c r="D77" s="19"/>
-      <c r="L77"/>
-    </row>
-    <row r="78" ht="24.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A78" s="18" t="s">
+      <c r="B77" s="20" t="s">
+        <v>138</v>
+      </c>
+      <c r="C77" s="20"/>
+      <c r="D77" s="20"/>
+      <c r="K77" s="4"/>
+      <c r="L77" s="4"/>
+    </row>
+    <row r="78" ht="19.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A78" s="19" t="s">
         <v>43</v>
       </c>
-      <c r="B78" s="19" t="s">
-        <v>138</v>
-      </c>
-      <c r="C78" s="19"/>
-      <c r="D78" s="19"/>
-      <c r="L78"/>
-    </row>
-    <row r="79" ht="24.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A79" s="18" t="s">
+      <c r="B78" s="20" t="s">
+        <v>139</v>
+      </c>
+      <c r="C78" s="20"/>
+      <c r="D78" s="20"/>
+      <c r="K78" s="4"/>
+      <c r="L78" s="4"/>
+    </row>
+    <row r="79" ht="19.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A79" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="B79" s="20" t="s">
-        <v>139</v>
-      </c>
-      <c r="C79" s="20"/>
-      <c r="D79" s="20"/>
-      <c r="L79"/>
-    </row>
-    <row r="80" ht="24.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A80" s="18" t="s">
+      <c r="B79" s="21" t="s">
+        <v>140</v>
+      </c>
+      <c r="C79" s="21"/>
+      <c r="D79" s="21"/>
+      <c r="K79" s="4"/>
+      <c r="L79" s="4"/>
+    </row>
+    <row r="80" ht="19.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A80" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="B80" s="19" t="s">
-        <v>140</v>
-      </c>
-      <c r="C80" s="19"/>
-      <c r="D80" s="19"/>
-      <c r="L80"/>
-    </row>
-    <row r="81" ht="24.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A81" s="18" t="s">
+      <c r="B80" s="20" t="s">
+        <v>141</v>
+      </c>
+      <c r="C80" s="20"/>
+      <c r="D80" s="20"/>
+      <c r="K80" s="4"/>
+      <c r="L80" s="4"/>
+    </row>
+    <row r="81" ht="19.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A81" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="B81" s="20" t="s">
-        <v>141</v>
-      </c>
-      <c r="C81" s="20"/>
-      <c r="D81" s="20"/>
-      <c r="L81"/>
-    </row>
-    <row r="82" ht="24.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A82" s="18" t="s">
+      <c r="B81" s="21" t="s">
+        <v>142</v>
+      </c>
+      <c r="C81" s="21"/>
+      <c r="D81" s="21"/>
+      <c r="K81" s="4"/>
+      <c r="L81" s="4"/>
+    </row>
+    <row r="82" ht="19.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A82" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="B82" s="20" t="s">
-        <v>142</v>
-      </c>
-      <c r="C82" s="20"/>
-      <c r="D82" s="20"/>
-      <c r="L82"/>
-    </row>
-    <row r="83" ht="24.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A83" s="18" t="s">
+      <c r="B82" s="21" t="s">
+        <v>143</v>
+      </c>
+      <c r="C82" s="21"/>
+      <c r="D82" s="21"/>
+      <c r="K82" s="4"/>
+      <c r="L82" s="4"/>
+    </row>
+    <row r="83" ht="19.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A83" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="B83" s="21" t="s">
-        <v>143</v>
-      </c>
-      <c r="C83" s="21"/>
-      <c r="D83" s="21"/>
-      <c r="K83" s="22" t="s">
+      <c r="B83" s="22" t="s">
+        <v>144</v>
+      </c>
+      <c r="C83" s="22"/>
+      <c r="D83" s="22"/>
+      <c r="K83" s="23" t="s">
         <v>92</v>
       </c>
-      <c r="L83" s="22"/>
-    </row>
-    <row r="84" ht="24.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A84" s="18" t="s">
+      <c r="L83" s="23"/>
+    </row>
+    <row r="84" ht="19.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A84" s="19" t="s">
         <v>56</v>
       </c>
-      <c r="B84" s="21" t="s">
-        <v>144</v>
-      </c>
-      <c r="C84" s="21"/>
-      <c r="D84" s="21"/>
-      <c r="K84" s="22" t="s">
+      <c r="B84" s="22" t="s">
+        <v>145</v>
+      </c>
+      <c r="C84" s="22"/>
+      <c r="D84" s="22"/>
+      <c r="K84" s="23" t="s">
         <v>92</v>
       </c>
-      <c r="L84" s="22"/>
-    </row>
-    <row r="85" ht="24.75" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A85" s="18" t="s">
+      <c r="L84" s="23"/>
+    </row>
+    <row r="85" ht="19.5" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A85" s="19" t="s">
         <v>58</v>
       </c>
-      <c r="B85" s="21" t="s">
-        <v>145</v>
-      </c>
-      <c r="C85" s="21"/>
-      <c r="D85" s="21"/>
-    </row>
-    <row r="86" ht="24.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B86" s="23" t="s">
+      <c r="B85" s="22" t="s">
         <v>146</v>
       </c>
-      <c r="C86" s="23"/>
-      <c r="D86" s="23"/>
-      <c r="E86" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="F86" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="G86" s="17" t="s">
+      <c r="C85" s="22"/>
+      <c r="D85" s="22"/>
+    </row>
+    <row r="86" ht="19.5" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B86" s="24" t="s">
+        <v>147</v>
+      </c>
+      <c r="C86" s="24"/>
+      <c r="D86" s="24"/>
+      <c r="E86" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="F86" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="G86" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="H86" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="I86" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="J86" s="17" t="s">
+      <c r="H86" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="I86" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="J86" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="L86"/>
-    </row>
-    <row r="87" ht="24.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A87" s="18" t="s">
+      <c r="K86" s="4"/>
+      <c r="L86" s="4"/>
+    </row>
+    <row r="87" ht="19.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A87" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="B87" s="19" t="s">
-        <v>147</v>
-      </c>
-      <c r="C87" s="19"/>
-      <c r="D87" s="19"/>
-      <c r="L87"/>
-    </row>
-    <row r="88" ht="24.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A88" s="18" t="s">
+      <c r="B87" s="20" t="s">
+        <v>148</v>
+      </c>
+      <c r="C87" s="20"/>
+      <c r="D87" s="20"/>
+      <c r="K87" s="4"/>
+      <c r="L87" s="4"/>
+    </row>
+    <row r="88" ht="19.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A88" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="B88" s="20" t="s">
-        <v>148</v>
-      </c>
-      <c r="C88" s="20"/>
-      <c r="D88" s="20"/>
-      <c r="L88"/>
-    </row>
-    <row r="89" ht="24.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A89" s="18" t="s">
+      <c r="B88" s="21" t="s">
+        <v>149</v>
+      </c>
+      <c r="C88" s="21"/>
+      <c r="D88" s="21"/>
+      <c r="K88" s="4"/>
+      <c r="L88" s="4"/>
+    </row>
+    <row r="89" ht="19.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A89" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="B89" s="20" t="s">
-        <v>149</v>
-      </c>
-      <c r="C89" s="20"/>
-      <c r="D89" s="20"/>
-      <c r="L89"/>
-    </row>
-    <row r="90" ht="24.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B90" s="23" t="s">
+      <c r="B89" s="21" t="s">
         <v>150</v>
       </c>
-      <c r="C90" s="23"/>
-      <c r="D90" s="23"/>
-      <c r="E90" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="F90" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="G90" s="17" t="s">
+      <c r="C89" s="21"/>
+      <c r="D89" s="21"/>
+      <c r="K89" s="4"/>
+      <c r="L89" s="4"/>
+    </row>
+    <row r="90" ht="19.5" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B90" s="24" t="s">
+        <v>151</v>
+      </c>
+      <c r="C90" s="24"/>
+      <c r="D90" s="24"/>
+      <c r="E90" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="F90" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="G90" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="H90" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="I90" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="J90" s="17" t="s">
+      <c r="H90" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="I90" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="J90" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="L90"/>
-    </row>
-    <row r="91" ht="24.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A91" s="18" t="s">
+      <c r="K90" s="4"/>
+      <c r="L90" s="4"/>
+    </row>
+    <row r="91" ht="19.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A91" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="B91" s="20" t="s">
-        <v>151</v>
-      </c>
-      <c r="C91" s="20"/>
-      <c r="D91" s="20"/>
-      <c r="L91"/>
-    </row>
-    <row r="92" ht="24.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A92" s="18" t="s">
+      <c r="B91" s="21" t="s">
+        <v>152</v>
+      </c>
+      <c r="C91" s="21"/>
+      <c r="D91" s="21"/>
+      <c r="K91" s="4"/>
+      <c r="L91" s="4"/>
+    </row>
+    <row r="92" ht="19.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A92" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="B92" s="20" t="s">
-        <v>152</v>
-      </c>
-      <c r="C92" s="20"/>
-      <c r="D92" s="20"/>
-      <c r="L92"/>
-    </row>
-    <row r="93" ht="24.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A93" s="18" t="s">
+      <c r="B92" s="21" t="s">
+        <v>153</v>
+      </c>
+      <c r="C92" s="21"/>
+      <c r="D92" s="21"/>
+      <c r="K92" s="4"/>
+      <c r="L92" s="4"/>
+    </row>
+    <row r="93" ht="19.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A93" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="B93" s="20" t="s">
-        <v>153</v>
-      </c>
-      <c r="C93" s="20"/>
-      <c r="D93" s="20"/>
-      <c r="L93"/>
-    </row>
-    <row r="94" ht="24.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A94" s="18" t="s">
+      <c r="B93" s="21" t="s">
+        <v>154</v>
+      </c>
+      <c r="C93" s="21"/>
+      <c r="D93" s="21"/>
+      <c r="K93" s="4"/>
+      <c r="L93" s="4"/>
+    </row>
+    <row r="94" ht="19.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A94" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="B94" s="20" t="s">
-        <v>154</v>
-      </c>
-      <c r="C94" s="20"/>
-      <c r="D94" s="20"/>
-      <c r="L94"/>
-    </row>
-    <row r="95" ht="24.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A95" s="18" t="s">
+      <c r="B94" s="21" t="s">
+        <v>155</v>
+      </c>
+      <c r="C94" s="21"/>
+      <c r="D94" s="21"/>
+      <c r="K94" s="4"/>
+      <c r="L94" s="4"/>
+    </row>
+    <row r="95" ht="19.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A95" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="B95" s="20" t="s">
-        <v>155</v>
-      </c>
-      <c r="C95" s="20"/>
-      <c r="D95" s="20"/>
-      <c r="L95"/>
-    </row>
-    <row r="96" ht="24.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A96" s="18" t="s">
+      <c r="B95" s="21" t="s">
+        <v>156</v>
+      </c>
+      <c r="C95" s="21"/>
+      <c r="D95" s="21"/>
+      <c r="K95" s="4"/>
+      <c r="L95" s="4"/>
+    </row>
+    <row r="96" ht="19.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A96" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="B96" s="20" t="s">
-        <v>156</v>
-      </c>
-      <c r="C96" s="20"/>
-      <c r="D96" s="20"/>
-      <c r="L96"/>
-    </row>
-    <row r="97" ht="24.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A97" s="18" t="s">
+      <c r="B96" s="21" t="s">
+        <v>157</v>
+      </c>
+      <c r="C96" s="21"/>
+      <c r="D96" s="21"/>
+      <c r="K96" s="4"/>
+      <c r="L96" s="4"/>
+    </row>
+    <row r="97" ht="19.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A97" s="19" t="s">
         <v>43</v>
       </c>
-      <c r="B97" s="20" t="s">
-        <v>157</v>
-      </c>
-      <c r="C97" s="20"/>
-      <c r="D97" s="20"/>
-      <c r="L97"/>
-    </row>
-    <row r="98" ht="24.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A98" s="18" t="s">
+      <c r="B97" s="21" t="s">
+        <v>158</v>
+      </c>
+      <c r="C97" s="21"/>
+      <c r="D97" s="21"/>
+      <c r="K97" s="4"/>
+      <c r="L97" s="4"/>
+    </row>
+    <row r="98" ht="19.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A98" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="B98" s="20" t="s">
-        <v>158</v>
-      </c>
-      <c r="C98" s="20"/>
-      <c r="D98" s="20"/>
-      <c r="L98"/>
-    </row>
-    <row r="99" ht="24.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A99" s="18" t="s">
+      <c r="B98" s="21" t="s">
+        <v>159</v>
+      </c>
+      <c r="C98" s="21"/>
+      <c r="D98" s="21"/>
+      <c r="K98" s="4"/>
+      <c r="L98" s="4"/>
+    </row>
+    <row r="99" ht="19.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A99" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="B99" s="20" t="s">
-        <v>159</v>
-      </c>
-      <c r="C99" s="20"/>
-      <c r="D99" s="20"/>
-      <c r="L99"/>
-    </row>
-    <row r="100" ht="24.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A100" s="18" t="s">
+      <c r="B99" s="21" t="s">
+        <v>160</v>
+      </c>
+      <c r="C99" s="21"/>
+      <c r="D99" s="21"/>
+      <c r="K99" s="4"/>
+      <c r="L99" s="4"/>
+    </row>
+    <row r="100" ht="19.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A100" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="B100" s="20" t="s">
-        <v>160</v>
-      </c>
-      <c r="C100" s="20"/>
-      <c r="D100" s="20"/>
-      <c r="L100"/>
-    </row>
-    <row r="101" ht="24.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A101" s="18" t="s">
+      <c r="B100" s="21" t="s">
+        <v>161</v>
+      </c>
+      <c r="C100" s="21"/>
+      <c r="D100" s="21"/>
+      <c r="K100" s="4"/>
+      <c r="L100" s="4"/>
+    </row>
+    <row r="101" ht="19.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A101" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="B101" s="20" t="s">
-        <v>161</v>
-      </c>
-      <c r="C101" s="20"/>
-      <c r="D101" s="20"/>
-      <c r="L101"/>
-    </row>
-    <row r="102" ht="24.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A102" s="18" t="s">
+      <c r="B101" s="21" t="s">
+        <v>162</v>
+      </c>
+      <c r="C101" s="21"/>
+      <c r="D101" s="21"/>
+      <c r="K101" s="4"/>
+      <c r="L101" s="4"/>
+    </row>
+    <row r="102" ht="19.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A102" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="B102" s="20" t="s">
-        <v>162</v>
-      </c>
-      <c r="C102" s="20"/>
-      <c r="D102" s="20"/>
-      <c r="L102"/>
-    </row>
-    <row r="103" ht="24.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A103" s="18" t="s">
+      <c r="B102" s="21" t="s">
+        <v>163</v>
+      </c>
+      <c r="C102" s="21"/>
+      <c r="D102" s="21"/>
+      <c r="K102" s="4"/>
+      <c r="L102" s="4"/>
+    </row>
+    <row r="103" ht="19.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A103" s="19" t="s">
         <v>56</v>
       </c>
-      <c r="B103" s="20" t="s">
-        <v>163</v>
-      </c>
-      <c r="C103" s="20"/>
-      <c r="D103" s="20"/>
-      <c r="L103"/>
-    </row>
-    <row r="104" ht="18" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A104" s="18" t="s">
+      <c r="B103" s="21" t="s">
+        <v>164</v>
+      </c>
+      <c r="C103" s="21"/>
+      <c r="D103" s="21"/>
+      <c r="K103" s="4"/>
+      <c r="L103" s="4"/>
+    </row>
+    <row r="104" ht="14.25" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A104" s="19" t="s">
         <v>58</v>
       </c>
-      <c r="B104" s="27" t="s">
-        <v>164</v>
-      </c>
-      <c r="C104" s="27"/>
-      <c r="D104" s="27"/>
-      <c r="L104"/>
-    </row>
-    <row r="105" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="106" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="107" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="108" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="109" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="110" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="111" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="112" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="113" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="114" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="115" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="116" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="117" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="118" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="119" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="120" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="121" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="122" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="123" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="124" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="125" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="126" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="127" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="128" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="129" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="130" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="131" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="132" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="133" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="134" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="135" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="136" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="137" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="138" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="139" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="140" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="141" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="142" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="143" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="144" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="145" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="146" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="147" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="148" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="149" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="150" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+      <c r="B104" s="28" t="s">
+        <v>165</v>
+      </c>
+      <c r="C104" s="28"/>
+      <c r="D104" s="28"/>
+      <c r="K104" s="4"/>
+      <c r="L104" s="4"/>
+    </row>
+    <row r="105" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <mergeCells count="216">
+  <mergeCells count="71">
     <mergeCell ref="A1:C3"/>
     <mergeCell ref="E1:F1"/>
     <mergeCell ref="G1:K1"/>
@@ -2728,181 +2763,51 @@
     <mergeCell ref="K29:L29"/>
     <mergeCell ref="B30:D30"/>
     <mergeCell ref="K30:L30"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="K31:L31"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="K32:L32"/>
-    <mergeCell ref="B33:D33"/>
-    <mergeCell ref="K33:L33"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="K34:L34"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="K35:L35"/>
-    <mergeCell ref="B36:D36"/>
-    <mergeCell ref="K36:L36"/>
-    <mergeCell ref="B37:D37"/>
-    <mergeCell ref="K37:L37"/>
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="K38:L38"/>
-    <mergeCell ref="B39:D39"/>
-    <mergeCell ref="K39:L39"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="K40:L40"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="K41:L41"/>
-    <mergeCell ref="B42:D42"/>
-    <mergeCell ref="B43:D43"/>
-    <mergeCell ref="B44:D44"/>
-    <mergeCell ref="K44:L44"/>
-    <mergeCell ref="B45:D45"/>
-    <mergeCell ref="K45:L45"/>
-    <mergeCell ref="B46:D46"/>
-    <mergeCell ref="K46:L46"/>
-    <mergeCell ref="B47:D47"/>
-    <mergeCell ref="K47:L47"/>
-    <mergeCell ref="B48:D48"/>
-    <mergeCell ref="K48:L48"/>
-    <mergeCell ref="B49:D49"/>
-    <mergeCell ref="K49:L49"/>
-    <mergeCell ref="B50:D50"/>
-    <mergeCell ref="K50:L50"/>
-    <mergeCell ref="B51:D51"/>
-    <mergeCell ref="K51:L51"/>
-    <mergeCell ref="B52:D52"/>
-    <mergeCell ref="K52:L52"/>
-    <mergeCell ref="B53:D53"/>
-    <mergeCell ref="K53:L53"/>
-    <mergeCell ref="B54:D54"/>
-    <mergeCell ref="K54:L54"/>
-    <mergeCell ref="B55:D55"/>
-    <mergeCell ref="K55:L55"/>
-    <mergeCell ref="B56:D56"/>
-    <mergeCell ref="K56:L56"/>
-    <mergeCell ref="B57:D57"/>
-    <mergeCell ref="K57:L57"/>
-    <mergeCell ref="B58:D58"/>
-    <mergeCell ref="K58:L58"/>
-    <mergeCell ref="B59:D59"/>
-    <mergeCell ref="K59:L59"/>
-    <mergeCell ref="B60:D60"/>
-    <mergeCell ref="K60:L60"/>
-    <mergeCell ref="B61:D61"/>
-    <mergeCell ref="K61:L61"/>
-    <mergeCell ref="B62:D62"/>
-    <mergeCell ref="K62:L62"/>
-    <mergeCell ref="B63:D63"/>
-    <mergeCell ref="K63:L63"/>
-    <mergeCell ref="B64:D64"/>
-    <mergeCell ref="K64:L64"/>
-    <mergeCell ref="B65:D65"/>
-    <mergeCell ref="K65:L65"/>
-    <mergeCell ref="B66:D66"/>
-    <mergeCell ref="K66:L66"/>
-    <mergeCell ref="B67:D67"/>
-    <mergeCell ref="K67:L67"/>
-    <mergeCell ref="B68:D68"/>
-    <mergeCell ref="K68:L68"/>
-    <mergeCell ref="B69:D69"/>
-    <mergeCell ref="K69:L69"/>
-    <mergeCell ref="B70:D70"/>
-    <mergeCell ref="K70:L70"/>
-    <mergeCell ref="B71:D71"/>
-    <mergeCell ref="K71:L71"/>
-    <mergeCell ref="B72:D72"/>
-    <mergeCell ref="K72:L72"/>
-    <mergeCell ref="B73:D73"/>
-    <mergeCell ref="K73:L73"/>
-    <mergeCell ref="B74:D74"/>
-    <mergeCell ref="K74:L74"/>
-    <mergeCell ref="B75:D75"/>
-    <mergeCell ref="K75:L75"/>
-    <mergeCell ref="B76:D76"/>
-    <mergeCell ref="K76:L76"/>
-    <mergeCell ref="B77:D77"/>
-    <mergeCell ref="K77:L77"/>
-    <mergeCell ref="B78:D78"/>
-    <mergeCell ref="K78:L78"/>
-    <mergeCell ref="B79:D79"/>
-    <mergeCell ref="K79:L79"/>
-    <mergeCell ref="B80:D80"/>
-    <mergeCell ref="K80:L80"/>
-    <mergeCell ref="B81:D81"/>
-    <mergeCell ref="K81:L81"/>
-    <mergeCell ref="B82:D82"/>
-    <mergeCell ref="K82:L82"/>
-    <mergeCell ref="B83:D83"/>
-    <mergeCell ref="K83:L83"/>
-    <mergeCell ref="B84:D84"/>
-    <mergeCell ref="K84:L84"/>
-    <mergeCell ref="B85:D85"/>
-    <mergeCell ref="B86:D86"/>
-    <mergeCell ref="K86:L86"/>
-    <mergeCell ref="B87:D87"/>
-    <mergeCell ref="K87:L87"/>
-    <mergeCell ref="B88:D88"/>
-    <mergeCell ref="K88:L88"/>
-    <mergeCell ref="B89:D89"/>
-    <mergeCell ref="K89:L89"/>
-    <mergeCell ref="B90:D90"/>
-    <mergeCell ref="K90:L90"/>
-    <mergeCell ref="B91:D91"/>
-    <mergeCell ref="K91:L91"/>
-    <mergeCell ref="B92:D92"/>
-    <mergeCell ref="K92:L92"/>
-    <mergeCell ref="B93:D93"/>
-    <mergeCell ref="K93:L93"/>
-    <mergeCell ref="B94:D94"/>
-    <mergeCell ref="K94:L94"/>
-    <mergeCell ref="B95:D95"/>
-    <mergeCell ref="K95:L95"/>
-    <mergeCell ref="B96:D96"/>
-    <mergeCell ref="K96:L96"/>
-    <mergeCell ref="B97:D97"/>
-    <mergeCell ref="K97:L97"/>
-    <mergeCell ref="B98:D98"/>
-    <mergeCell ref="K98:L98"/>
-    <mergeCell ref="B99:D99"/>
-    <mergeCell ref="K99:L99"/>
-    <mergeCell ref="B100:D100"/>
-    <mergeCell ref="K100:L100"/>
-    <mergeCell ref="B101:D101"/>
-    <mergeCell ref="K101:L101"/>
-    <mergeCell ref="B102:D102"/>
-    <mergeCell ref="K102:L102"/>
-    <mergeCell ref="B103:D103"/>
-    <mergeCell ref="K103:L103"/>
-    <mergeCell ref="B104:D104"/>
-    <mergeCell ref="K104:L104"/>
   </mergeCells>
-  <dataValidations count="10">
+  <dataValidations count="15">
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E10:J46">
+      <formula1>"√,×,/,待"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E100:I105">
+      <formula1>"√,×,/,待"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E48:J50">
+      <formula1>"√,×,/,待"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E52:J53">
+      <formula1>"√,×,/,待"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E55:J59">
+      <formula1>"√,×,/,待"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E61:I70">
+      <formula1>"√,×,/,待"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E72:I85">
+      <formula1>"√,×,/,待"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E87:I89">
+      <formula1>"√,×,/,待"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E9:J46">
+      <formula1>"√,×,/,待"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E91:I105">
+      <formula1>"√,×,/,待"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="J100:J104">
       <formula1>"√,×,无"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E100:J104">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="J61:J70">
       <formula1>"√,×,无"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E48:J50">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="J72:J85">
       <formula1>"√,×,无"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E52:J53">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="J87:J89">
       <formula1>"√,×,无"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E55:J59">
-      <formula1>"√,×,无"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E61:J70">
-      <formula1>"√,×,无"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E72:J85">
-      <formula1>"√,×,无"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E87:J89">
-      <formula1>"√,×,无"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E9:J46">
-      <formula1>"√,×,无"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E91:J104">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="J91:J104">
       <formula1>"√,×,无"</formula1>
     </dataValidation>
   </dataValidations>
